--- a/마약/비치향정,마약현황.xlsx
+++ b/마약/비치향정,마약현황.xlsx
@@ -1823,7 +1823,7 @@
         <xdr:cNvPr id="3" name="직사각형 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2185,8 +2185,10 @@
     <col min="3" max="3" width="32.5546875" style="2" customWidth="1"/>
     <col min="4" max="4" width="5.44140625" style="55" customWidth="1"/>
     <col min="5" max="6" width="6.88671875" style="55" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" style="55" customWidth="1"/>
-    <col min="8" max="35" width="6.88671875" style="55" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="55" customWidth="1"/>
+    <col min="8" max="10" width="6.88671875" style="55" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" style="55" customWidth="1"/>
+    <col min="12" max="35" width="6.88671875" style="55" customWidth="1"/>
     <col min="36" max="36" width="9" style="55" bestFit="1" customWidth="1"/>
     <col min="37" max="38" width="6.6640625" style="2" customWidth="1"/>
     <col min="39" max="16384" width="8.88671875" style="2"/>
@@ -3819,7 +3821,7 @@
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.47244094488188981" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="43" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>

--- a/마약/비치향정,마약현황.xlsx
+++ b/마약/비치향정,마약현황.xlsx
@@ -1801,90 +1801,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>452437</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>23811</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>428624</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>398318</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="직사각형 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11191408" y="7494399"/>
-          <a:ext cx="8940892" cy="3642890"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="2800" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="나눔스퀘어_ac Bold" panose="020B0600000101010101" pitchFamily="50" charset="-127"/>
-              <a:ea typeface="나눔스퀘어_ac Bold" panose="020B0600000101010101" pitchFamily="50" charset="-127"/>
-            </a:rPr>
-            <a:t>특수병동 일련번호 확인하기</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2800" baseline="0">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-            <a:latin typeface="나눔스퀘어_ac Bold" panose="020B0600000101010101" pitchFamily="50" charset="-127"/>
-            <a:ea typeface="나눔스퀘어_ac Bold" panose="020B0600000101010101" pitchFamily="50" charset="-127"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3823,6 +3739,5 @@
   <pageMargins left="0.23622047244094491" right="0.47244094488188981" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>